--- a/assets/constructions/examples/ctd_tmfe_holder.xlsx
+++ b/assets/constructions/examples/ctd_tmfe_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,21 +614,41 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NSL203D</t>
+          <t>GTBL2525M22-35L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TopThread / TopGroove</t>
+          <t>GT*R/L-L</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,40 +658,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03_WID</t>
+          <t>TGF22_H</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>N.3L</t>
+          <t>TGF22R/L</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ISO_5610:31.75X31.75</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>WIDIA_N03</t>
+          <t>DER_TGF22H</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>L</t>
@@ -679,24 +697,22 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>5.334</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -704,25 +720,23 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>31.75</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>31.75</v>
+        <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.1</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>152.4</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
@@ -730,9 +744,15 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Turning Catalogue</t>
-        </is>
-      </c>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -742,7 +762,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GVNE90L20-26</t>
+          <t>GVEL20-29-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -762,7 +782,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VAR_GVNE_26</t>
+          <t>VAR_GVE_29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -778,11 +798,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VARGUS_GVN:26R</t>
+          <t>VARGUS_GVN:29L</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -825,18 +845,20 @@
         <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.5</v>
+        <v>14.2</v>
       </c>
       <c r="AA3" t="n">
         <v>125</v>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>8</v>
+      </c>
       <c r="AG3" t="b">
         <v>1</v>
       </c>
@@ -850,21 +872,35 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170.78</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>15700.44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GVEL16-29-1</t>
+          <t>NSR2020K2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GVN</t>
+          <t>TopThread / TopGroove</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -879,23 +915,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VAR_GVE_29</t>
+          <t>02_WID</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N.2R</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ISO_5610:16X16</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>VARGUS_GVN:29L</t>
+          <t>WIDIA_N02</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -906,26 +946,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>3.51</v>
+      </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
@@ -936,26 +976,22 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.2</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>125</v>
       </c>
-      <c r="AB4" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>1</v>
       </c>
@@ -966,9 +1002,15 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2020 / WIDIA Turning Catalogue</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -978,7 +1020,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GVEL16-29-2</t>
+          <t>GVE90R20-29-2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1009,7 +1051,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ISO_5610:16X16</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1018,14 +1060,14 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -1055,25 +1097,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.2</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
         <v>125</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.2</v>
+        <v>20.2</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AG5" t="b">
         <v>1</v>
@@ -1088,6 +1130,20 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>17894.89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1097,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GVNE90R25-29-1</t>
+          <t>GVNER100-29-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GVN</t>
+          <t>GVNE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1116,20 +1172,24 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:25.4X25.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>VARGUS_GVN:29L</t>
+          <t>VARGUS_GVN:29R</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1155,9 +1215,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="b">
         <v>0</v>
       </c>
@@ -1168,32 +1226,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>33</v>
+        <v>25.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>152.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>25</v>
-      </c>
+        <v>17.75</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AG6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1204,6 +1258,20 @@
         <is>
           <t>2021/Groovex Vargus</t>
         </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>203</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>18662.54</v>
       </c>
     </row>
   </sheetData>
